--- a/Cronograma_NOTURNO.xlsx
+++ b/Cronograma_NOTURNO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,33 +461,38 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>COORIENTADOR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>ALUNO_ORIENTADO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TITULO TCC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MEMBRO 1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MEMBRO 2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>MEMBRO 3</t>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TILSP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -516,36 +521,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Joseanne Kanufre Pires Ferreira</t>
-        </is>
+          <t>Marco Aurélio de Souza</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v/>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
+          <t>Leonilda de Oliveira Antunes</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Juliana Ristow Canuto</t>
+          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jannefer Desselman</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
+          <t>Ligia Paula Couto</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Thiago Alexandre Correa</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -574,30 +582,33 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Keli Cristina Pacheco</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ellen Andrade </t>
-        </is>
+          <t>Joana dArc Martins Pupo</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v/>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
+          <t>Lidiane Patrine Mendes Batista</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Jane Kelly de Oliveira</t>
+          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Carlos André Ferreira</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
+          <t>Cloris Porto Torquato</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Névio de Campos</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v/>
       </c>
     </row>
@@ -635,33 +646,36 @@
           <t>Andressa França</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>CINTIA PIRES SZCZEREPA</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Estudantes surdos na transição para os anos finais: análise documental do PPP de uma escola estadual em Ponta Grossa/PR</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Rúbia Carla da Silva</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Eliane Santos Raupp</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -685,41 +699,44 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cloris Porto Torquato </t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guilherme Mayer Axt </t>
-        </is>
+          <t xml:space="preserve">Keli Cristina Pacheco </t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v/>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
+          <t>Ana Carolina Troyner Yamamoto</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Alyda Henrietta Zomer</t>
+          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Giuliano Lellis Ito Santos</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
+          <t>Eunice de Morais</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Daiane Cristina Pereira</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -743,41 +760,46 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
+          <t>Bhianca Moro Portella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leonilda de Oliveira Antunes</t>
+          <t>Fabiana Simeoni Avais</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
+          <t>Alanis Cristine Barros</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ligia Paula Couto</t>
+          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Thiago Alexandre Correa</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+          <t>João Victor Chiquetto Silva</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ana Letícia Carneiro de Oliveira</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -801,41 +823,44 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fabiana Simeoni Avais</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Heridiano Pacheco dos Santos</t>
-        </is>
+          <t>Rosangela Schardong</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v/>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
+          <t>Rodrigo Vaz Alvarez Gonzales</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Rubia Carla da Silva</t>
+          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Alyda Zomer</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
+          <t>Giuliano Lellis Ito Santos</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Lincoln Felipe Freitas</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -864,36 +889,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rosangela Schardong</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Estefany Ferreira Carvalho</t>
-        </is>
+          <t>Evanir Pavloski</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v/>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
+          <t>Ana Julia Ruths de Castro</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeska Gracioso Carlos </t>
+          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Lincoln Felipe Freitas</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+          <t>Deborah Scheidt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Eunice de Morais</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -917,41 +945,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Joana dArc Martins Pupo</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Lidiane Patrine Mendes Batista</t>
-        </is>
+          <t>Charlott Eloize Leviski</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v/>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
+          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Clóris Porto Torquato</t>
+          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Névio de Campos</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+          <t>Simone de Fátima Colman Martins</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Juliana Ristow Canuto</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -980,36 +1011,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>EMANUELLY MAUDA SCOS</t>
-        </is>
+          <t>Andressa França</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v/>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JOGOS NO ENSINO DE LIBRAS COMO PRIMEIRA LÍNGUA NO ENSINO FUNDAMENTAL BILÍNGUE DE SURDOS: ANÁLISE DOCUMENTAL DO SWOP</t>
+          <t>NÚBIA DE BRAGA COTA MENDES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Andressa França</t>
+          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Joyce Cristina Souza</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+          <t>Vinícius Heitor Pereira</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sandra Cristina Demschinski</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1033,41 +1067,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
-        </is>
+          <t>Keli Cristina Pacheco</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v/>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
+          <t xml:space="preserve">Ellen Andrade </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Simone de Fátima Colman Martins</t>
+          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Juliana Ristow Canuto</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+          <t>Jane Kelly de Oliveira</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Carlos André Ferreira</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1091,38 +1128,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LIBRAS</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vinícius Heitor Pereira</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Andréia Rosane Bueno da Silva</t>
-        </is>
+          <t>Fabiana Simeoni Avais</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v/>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
+          <t>Heridiano Pacheco dos Santos</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine Fischer </t>
+          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Carlos André Ferreira</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Precisa de TILSP pois terá uma professora surda na banca</t>
-        </is>
+          <t>Ályda Henrietta Zomer</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1159,33 +1197,36 @@
           <t>Daiane Cristina Pereira</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>FERNANDA DA LUZ BATISTA</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Mulheres negras, violência e resistência: corpo, voz e autonomia em dois contos de Conceição Evaristo</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Giuliano Lellis Ito Santos</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Patricia Barreto Mainardi Maeso </t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1204,46 +1245,49 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Patricia Barreto Mainardi Maeso</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Giulliana Pinheiro</t>
-        </is>
+          <t>Marco Aurélio de Souza</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v/>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SMALL WONDERS: MATERIAL DIDÁTICO PARA O ENSINO BILÍNGUE DE CRIANÇAS DE 6 A 7 ANOS BASEADO NA ABORDAGEM COMMUNICATIVE LANGUAGE TEACHING</t>
+          <t>Rafael Milek Weinert</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Isabel Cristina Vollet Marson</t>
+          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deborah Scheidt </t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+          <t>Evanir Pavloski</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Felipe Teodoro da Silva</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1262,46 +1306,49 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rosangela Schardong</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Rodrigo Vaz Alvarez Gonzales</t>
-        </is>
+          <t xml:space="preserve">Cloris Porto Torquato </t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v/>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
+          <t xml:space="preserve">Guilherme Mayer Axt </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ályda Henrietta Zomer</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>Giuliano Lellis Ito Santos</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Lincoln Felipe Freitas</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1320,46 +1367,49 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LIBRAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keli Cristina Pacheco </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Ana Carolina Troyner Yamamoto</t>
-        </is>
+          <t>Vinícius Heitor Pereira</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v/>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
+          <t>VICTOR HENRIQUE DANILENKO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Eunice de Morais</t>
+          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
+          <t xml:space="preserve">Andressa França </t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Izabele Caroline Rodrigues Gomes</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1378,48 +1428,51 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LIBRAS</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva e Djane Antonucci Correa</t>
+          <t xml:space="preserve">Marcos Barbosa Carreira </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
+          <t>Fabiana Simeoni Avais</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUJEITOS NEGROS SURDOS E POLÍTICAS EDUCACIONAIS: UMA ANÁLISE DE DOCUMENTOS E MATERIAIS INSTITUCIONAIS FEDERAIS E PARANAENSES </t>
+          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cloris Porto Torquato</t>
+          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Katherine Fischer</t>
+          <t>Diogo Simão</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>TILSP - Valdemir Pontes Vieira</t>
-        </is>
+          <t>Álvaro Kasuaki Fujihara</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1438,50 +1491,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LIBRAS</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vinícius Heitor Pereira</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>VICTOR HENRIQUE DANILENKO</t>
-        </is>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v/>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
+          <t>Juliana da Silva Carneiro</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andressa França </t>
+          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Izabele Caroline Rodrigues Gomes</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
+          <t>Gisele Maciel</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Márcia Cristina do Carmo</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1491,12 +1547,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1506,40 +1562,43 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Rafael Milek Weinert</t>
-        </is>
+          <t>Silvana Oliveira</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v/>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
+          <t>Naiane Maria de Lima</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Evanir Pavloski</t>
+          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Felipe Teodoro da Silva</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+          <t>Lincoln Felipe Freitas</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Daiane Cristina Pereira</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1549,12 +1608,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1564,38 +1623,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Juliana da Silva Carneiro</t>
-        </is>
+          <t>Valeska Gracioso Carlos</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v/>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
+          <t>ESTELA MARTINS EIDAM</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Márcia Cristina do Carmo</t>
+          <t>Lucimar Araujo Braga</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Gisele Maciel</t>
-        </is>
+          <t xml:space="preserve">Marina Zavadzki </t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1614,46 +1674,49 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LIBRAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Evanir Pavloski</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Andrey Eduardo Malinoscky</t>
-        </is>
+          <t>Rúbia Carla da Silva</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v/>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
+          <t>EMANUELLY MAUDA SCOS</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Giuliano Lellis dos Santos</t>
+          <t>JOGOS NO ENSINO DE LIBRAS COMO PRIMEIRA LÍNGUA NO ENSINO FUNDAMENTAL BILÍNGUE DE SURDOS: ANÁLISE DOCUMENTAL DO SWOP</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Keli Cristina Pacheco</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+          <t>Andressa França</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Joyce Cristina Souza</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1672,46 +1735,49 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LIBRAS</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Andressa França</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>NÚBIA DE BRAGA COTA MENDES</t>
-        </is>
+          <t>Evanir Pavloski</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
+          <t>Andrey Eduardo Malinoscky</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Vinicius Heitor Pereira</t>
+          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sandra Cristina Demschinski</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+          <t>Giuliano Lellis Ito Santos</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Keli Cristina Pacheco</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1730,7 +1796,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1740,38 +1806,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bhianca Moro Portella</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Alanis Cristine Barros</t>
-        </is>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v/>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
+          <t>Julia  Soares Nadal</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>João Victor Chiquetto Silva</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Ana Letícia Carneiro de Oliveira</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabiana Simeoni Avais (Co-orientadora) </t>
-        </is>
+          <t>Cloris Porto Torquato</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1790,46 +1857,51 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LIBRAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Isabela Fernandes</t>
-        </is>
+          <t>Vinícius Heitor Pereira</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v/>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
+          <t>Andréia Rosane Bueno da Silva</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giuliano Lellis Ito Santos </t>
+          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Eunice de Morais</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v/>
+          <t xml:space="preserve">Katherine Fischer </t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Carlos André Ferreira</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Cristiane Ribeiro Rocha</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1853,41 +1925,44 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos André Ferreira </t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
-        </is>
+          <t>Charlott Eloize Leviski</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v/>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
+          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lincoln Felipe Freitas</t>
+          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+          <t>Fabiana Simeoni Avais</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bhianca Moro Portella</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1911,41 +1986,44 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Valeska Gracioso Carlos</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>ESTELA MARTINS EIDAM</t>
-        </is>
+          <t>Daniel van der Broocke de Oliveira Gomes</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v/>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
+          <t>Lohan Vinícius de Oliveira</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Lucimar Araujo Braga</t>
+          <t>A POEIRA NO RAIO DE SOL: LUCRÉCIO E A LONGA DURAÇÃO DO ATOMISMO</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marina Zavadzki </t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+          <t>Jane Kelly de Oliveira</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Eduardo Reis de Mello</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1974,36 +2052,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Evanir Pavloski</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Ana Julia Ruths de Castro</t>
-        </is>
+          <t>Andréa Correa Paraiso Müller</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v/>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
+          <t>Nicole Cristina Pokczyva</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Deborah Scheidt</t>
+          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Eunice de Morais</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+          <t>Daiane Cristina Pereira</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Paola Scheifer</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2027,41 +2108,44 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daniel van der Broocke de Oliveira Gomes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Lohan Vinícius de Oliveira</t>
-        </is>
+          <t>Patricia Barreto Mainardi Maeso</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v/>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A POEIRA NO RAIO DE SOL: LUCRÉCIO E A LONGA DURAÇÃO DO ATOMISMO</t>
+          <t>Giulliana Pinheiro</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Jane Kelly de Oliveira</t>
+          <t>SMALL WONDERS: MATERIAL DIDÁTICO PARA O ENSINO BILÍNGUE DE CRIANÇAS DE 6 A 7 ANOS BASEADO NA ABORDAGEM COMMUNICATIVE LANGUAGE TEACHING</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Eduardo Reis de Mello</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
+          <t>Isabel Cristina Vollet Marson</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deborah Scheidt </t>
+        </is>
+      </c>
+      <c r="M28" t="n">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2093,35 +2177,38 @@
           <t>Andressa França</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
-        </is>
+      <c r="H29" t="n">
+        <v/>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
+          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Katherine Fischer</t>
+          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva</t>
+          <t>Maria Auxiliadora Bezerra de Araújo</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TILSP - Valdemir </t>
+          <t>Joyce Cristina Souza</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Marcelo Oliveira Bleme</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2145,41 +2232,44 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
-        </is>
+          <t>Rosana Apolonia Harmuch</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v/>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
+          <t>Oziel dos Santos Martins</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fabiana Simeoni Avais</t>
+          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Bhianca Moro Portela</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
+          <t>Bianca Meira Lopes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Marco Aurélio de Souza</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2203,41 +2293,48 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LIBRAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Silvana Oliveira</t>
+          <t xml:space="preserve">Rúbia Carla da Silva </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Naiane Maria de Lima</t>
+          <t>Djane Antonucci Correa</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
+          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>LINCOLN FELIPE FREITAS</t>
+          <t xml:space="preserve">SUJEITOS NEGROS SURDOS E POLÍTICAS EDUCACIONAIS: UMA ANÁLISE DE DOCUMENTOS E MATERIAIS INSTITUCIONAIS FEDERAIS E PARANAENSES </t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v/>
+          <t>Cloris Porto Torquato</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Katherine Fischer</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Valdemir Pontes Vieira</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2266,36 +2363,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rosana Apolonia Harmuch</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Oziel dos Santos Martins</t>
-        </is>
+          <t xml:space="preserve">Carlos André Ferreira </t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v/>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
+          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Bianca Meira Lopes</t>
+          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+          <t>Lincoln Felipe Freitas</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Charlott Eloize Leviski</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2319,43 +2419,44 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
-        </is>
+          <t>Eunice de Morais</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v/>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
+          <t>Jackson Yuri Machado de Paula</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Cloris Porto Torquato</t>
+          <t>Leonardo S. Carrera Guisantes</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>João Victor Chiquetto Silva</t>
-        </is>
+          <t>Fatima Maria Aparecida Ruvinski Kusma</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2384,36 +2485,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Eunice de Morais</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Jackson Yuri Machado de Paula</t>
-        </is>
+          <t>Rosangela Schardong</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v/>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
+          <t>Estefany Ferreira Carvalho</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Leonardo S. Carrera Guisantes</t>
+          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Fatima Maria Aparecida Ruvinski Kusma (PPGEL)</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
+          <t xml:space="preserve">Valeska Gracioso Carlos </t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Lincoln Felipe Freitas</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2445,35 +2549,38 @@
           <t>Andressa França</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
-        </is>
+      <c r="H35" t="n">
+        <v/>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
+          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Maria Auxiliadora Bezerra de Araújo</t>
+          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Joyce Cristina Souza</t>
+          <t>Katherine Fischer</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>TILSP Marcelo Bleme</t>
+          <t>Rúbia Carla da Silva</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Valdemir Pontes Vieira</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2497,43 +2604,44 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Marcos Barbosa Carreira</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
-        </is>
+          <t>Daiane Cristina Pereira</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v/>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
+          <t>Isabela Fernandes</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Diogo Simão</t>
+          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Álvaro Kasuaki Fujihara</t>
+          <t xml:space="preserve">Giuliano Lellis Ito Santos </t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabiana Simeoni Avais (Co-orientadora) </t>
-        </is>
+          <t>Eunice de Morais</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2557,35 +2665,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LITERATURA</t>
+          <t>LINGUÍSTICA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Nicole Cristina Pokczyva</t>
-        </is>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v/>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
+          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
+          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Paola Scheifer</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
+          <t>João Victor Chiquetto Silva</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Cloris Porto Torquato</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
         <v/>
       </c>
     </row>
@@ -2623,33 +2734,36 @@
           <t>Evanir Pavloski</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="n">
+        <v/>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Hiago Neto Soares</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>“VÓS SOIS FILHOS DO DIABO” – A DESCONSTRUÇÃO DA UTOPIA PURITANA A PARTIR DA INTERTEXTUALIDADE BÍBLICA EM  “YOUNG GOODMAN BROWN”</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Déborah Scheidt</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>Deborah Scheidt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>Diego Gomes do Valle</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2673,38 +2787,39 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LINGUÍSTICA</t>
+          <t>LITERATURA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Julia  Soares Nadal</t>
-        </is>
+          <t>Andréa Correa Paraiso Müller</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v/>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
+          <t>Joseanne Kanufre Pires Ferreira</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Cloris Porto Torquato</t>
+          <t>Juliana Ristow Canuto</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>João Victor Chiquetto Silva</t>
-        </is>
+          <t>Jannefer Desselman</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2718,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,7 +2881,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alyda Henrietta Zomer</t>
+          <t>Ana Letícia Carneiro de Oliveira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2786,7 +2901,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2796,19 +2911,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guilherme Mayer Axt </t>
+          <t>Alanis Cristine Barros</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
+          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alyda Zomer</t>
+          <t>Andressa França</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2828,34 +2943,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Heridiano Pacheco dos Santos</t>
+          <t>CINTIA PIRES SZCZEREPA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
+          <t>Estudantes surdos na transição para os anos finais: análise documental do PPP de uma escola estadual em Ponta Grossa/PR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ana Letícia Carneiro de Oliveira</t>
+          <t>Andressa França</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2865,27 +2980,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alanis Cristine Barros</t>
+          <t>NÚBIA DE BRAGA COTA MENDES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
+          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
         </is>
       </c>
     </row>
@@ -2907,27 +3022,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CINTIA PIRES SZCZEREPA</t>
+          <t>VICTOR HENRIQUE DANILENKO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Estudantes surdos na transição para os anos finais: análise documental do PPP de uma escola estadual em Ponta Grossa/PR</t>
+          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
         </is>
       </c>
     </row>
@@ -2939,7 +3054,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2949,12 +3064,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2981,7 +3096,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2991,27 +3106,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>VICTOR HENRIQUE DANILENKO</t>
+          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
+          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3148,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3048,19 +3163,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NÚBIA DE BRAGA COTA MENDES</t>
+          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
+          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Andressa França</t>
+          <t>Andréa Correa Paraiso Müller</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3080,7 +3195,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3090,19 +3205,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
+          <t>Nicole Cristina Pokczyva</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
+          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Andressa França</t>
+          <t>Andréa Correa Paraiso Müller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3122,7 +3237,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3132,19 +3247,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
+          <t>Joseanne Kanufre Pires Ferreira</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
+          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
+          <t>Bhianca Moro Portella</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3164,7 +3279,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3174,19 +3289,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Joseanne Kanufre Pires Ferreira</t>
+          <t>Alanis Cristine Barros</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
+          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
+          <t>Bhianca Moro Portella</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3201,34 +3316,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nicole Cristina Pokczyva</t>
+          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
+          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bhianca Moro Portela</t>
+          <t>Bianca Meira Lopes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3258,24 +3373,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
+          <t>Oziel dos Santos Martins</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
+          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bhianca Moro Portella</t>
+          <t>Carlos André Ferreira</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3285,34 +3400,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alanis Cristine Barros</t>
+          <t xml:space="preserve">Ellen Andrade </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
+          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bianca Meira Lopes</t>
+          <t>Carlos André Ferreira</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3327,12 +3442,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3342,12 +3457,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Oziel dos Santos Martins</t>
+          <t>Andréia Rosane Bueno da Silva</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
+          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3474,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3369,34 +3484,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellen Andrade </t>
+          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
+          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carlos André Ferreira</t>
+          <t>Charlott Eloize Leviski</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3416,29 +3531,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Andréia Rosane Bueno da Silva</t>
+          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
+          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carlos André Ferreira</t>
+          <t>Charlott Eloize Leviski</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3468,12 +3583,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
+          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
+          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3600,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3505,29 +3620,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
+          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
+          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
+          <t>Cloris Porto Torquato</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3542,7 +3657,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3552,24 +3667,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
+          <t>Lidiane Patrine Mendes Batista</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
+          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
+          <t>Cloris Porto Torquato</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3579,12 +3694,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3594,12 +3709,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
+          <t xml:space="preserve">Guilherme Mayer Axt </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
+          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3726,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3626,22 +3741,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guilherme Mayer Axt </t>
+          <t>Julia  Soares Nadal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
+          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
         </is>
       </c>
     </row>
@@ -3653,7 +3768,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3663,7 +3778,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3705,12 +3820,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3732,7 +3847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloris Porto Torquato</t>
+          <t>Cristiane Ribeiro Rocha</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3747,34 +3862,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>TILSP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Julia  Soares Nadal</t>
+          <t>Andréia Rosane Bueno da Silva</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
+          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clóris Porto Torquato</t>
+          <t>Daiane Cristina Pereira</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3789,12 +3904,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3804,12 +3919,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lidiane Patrine Mendes Batista</t>
+          <t>Ana Carolina Troyner Yamamoto</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
+          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3978,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3873,12 +3988,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3888,12 +4003,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ana Carolina Troyner Yamamoto</t>
+          <t>Naiane Maria de Lima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
+          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
         </is>
       </c>
     </row>
@@ -3915,27 +4030,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Isabela Fernandes</t>
+          <t>Nicole Cristina Pokczyva</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
+          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
         </is>
       </c>
     </row>
@@ -3957,34 +4072,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Naiane Maria de Lima</t>
+          <t>Isabela Fernandes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
+          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
+          <t>Daniel van der Broocke de Oliveira Gomes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3999,39 +4114,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nicole Cristina Pokczyva</t>
+          <t>Lohan Vinícius de Oliveira</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
+          <t>A POEIRA NO RAIO DE SOL: LUCRÉCIO E A LONGA DURAÇÃO DO ATOMISMO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Daniel van der Broocke de Oliveira Gomes</t>
+          <t>Deborah Scheidt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4051,17 +4166,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lohan Vinícius de Oliveira</t>
+          <t>Ana Julia Ruths de Castro</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>A POEIRA NO RAIO DE SOL: LUCRÉCIO E A LONGA DURAÇÃO DO ATOMISMO</t>
+          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4188,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4083,12 +4198,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4125,12 +4240,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4140,12 +4255,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ana Julia Ruths de Castro</t>
+          <t>Hiago Neto Soares</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
+          <t>“VÓS SOIS FILHOS DO DIABO” – A DESCONSTRUÇÃO DA UTOPIA PURITANA A PARTIR DA INTERTEXTUALIDADE BÍBLICA EM  “YOUNG GOODMAN BROWN”</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4314,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4214,7 +4329,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4236,7 +4351,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Déborah Scheidt</t>
+          <t>Djane Antonucci Correa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4251,27 +4366,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Coorientador</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hiago Neto Soares</t>
+          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>“VÓS SOIS FILHOS DO DIABO” – A DESCONSTRUÇÃO DA UTOPIA PURITANA A PARTIR DA INTERTEXTUALIDADE BÍBLICA EM  “YOUNG GOODMAN BROWN”</t>
+          <t xml:space="preserve">SUJEITOS NEGROS SURDOS E POLÍTICAS EDUCACIONAIS: UMA ANÁLISE DE DOCUMENTOS E MATERIAIS INSTITUCIONAIS FEDERAIS E PARANAENSES </t>
         </is>
       </c>
     </row>
@@ -4293,12 +4408,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4377,12 +4492,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4409,7 +4524,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4419,12 +4534,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4434,12 +4549,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Isabela Fernandes</t>
+          <t>Ana Julia Ruths de Castro</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
+          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
         </is>
       </c>
     </row>
@@ -4466,22 +4581,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ana Julia Ruths de Castro</t>
+          <t>Jackson Yuri Machado de Paula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
+          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
         </is>
       </c>
     </row>
@@ -4508,22 +4623,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Jackson Yuri Machado de Paula</t>
+          <t>Isabela Fernandes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
+          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
         </is>
       </c>
     </row>
@@ -4545,27 +4660,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rafael Milek Weinert</t>
+          <t>Ana Julia Ruths de Castro</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
+          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4692,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4587,27 +4702,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Andrey Eduardo Malinoscky</t>
+          <t>Rafael Milek Weinert</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
+          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
         </is>
       </c>
     </row>
@@ -4629,12 +4744,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4644,12 +4759,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ana Julia Ruths de Castro</t>
+          <t>Andrey Eduardo Malinoscky</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Entre a vida e a obra: autoficção e crítica ao thatcherismo em A história de  Shuggie Bain, de Douglas Stuart.</t>
+          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
         </is>
       </c>
     </row>
@@ -4718,22 +4833,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Coorientador</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Heridiano Pacheco dos Santos</t>
+          <t>Alanis Cristine Barros</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
+          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4860,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4755,27 +4870,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alanis Cristine Barros</t>
+          <t>Heridiano Pacheco dos Santos</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>&lt;&lt;Sem-titulo ESTAMOS DEFININDO&gt;&gt;</t>
+          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4902,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4797,27 +4912,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Coorientador</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
+          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
+          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4954,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4854,12 +4969,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
+          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
+          <t>A PLATAFORMIZAÇÃO DO ENSINO DE LÍNGUA INGLESA NA REDE PÚBLICA DO PARANÁ E SEUS IMPACTOS NA AUTONOMIA DOCENTE E NO APRENDIZADO</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4996,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4928,7 +5043,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5012,7 +5127,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5022,12 +5137,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guilherme Mayer Axt </t>
+          <t>Rodrigo Vaz Alvarez Gonzales</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
+          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5211,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5106,12 +5221,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rodrigo Vaz Alvarez Gonzales</t>
+          <t xml:space="preserve">Guilherme Mayer Axt </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
+          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5253,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5148,19 +5263,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Isabela Fernandes</t>
+          <t>Andrey Eduardo Malinoscky</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
+          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Giuliano Lellis dos Santos</t>
+          <t>Giuliano Lellis Ito Santos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5175,12 +5290,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5190,12 +5305,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Andrey Eduardo Malinoscky</t>
+          <t>Isabela Fernandes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>OS LIMITES DA UTOPIA: EUGENIA, RAÇA E NECROPOLÍTICA EM  O PRESIDENTE NEGRO, DE MONTEIRO LOBATO</t>
+          <t>As marcas de ausência na construção da narradora-personagem em O Peso do pássaro morto.</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5217,12 +5332,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5301,12 +5416,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5343,12 +5458,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5375,7 +5490,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5385,12 +5500,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5427,7 +5542,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5459,7 +5574,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5469,12 +5584,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5511,7 +5626,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5543,7 +5658,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5558,7 +5673,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5595,12 +5710,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5610,12 +5725,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
+          <t>Julia  Soares Nadal</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
+          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
         </is>
       </c>
     </row>
@@ -5642,7 +5757,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5652,12 +5767,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Julia  Soares Nadal</t>
+          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">A concepção de PLAc e o papel do docente </t>
+          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5794,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5694,12 +5809,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Joseanne Kanufre Pires Ferreira</t>
+          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
+          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5826,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5721,12 +5836,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5736,12 +5851,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pamela Cristina Rodrigues </t>
+          <t>Joseanne Kanufre Pires Ferreira</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ENTRE O CUIDADO E O DIREITO À EDUCAÇÃO: DISCURSOS SOBRE INTERRUPÇÃO, RETORNO E PERMANÊNCIA ESCOLAR EM NARRATIVAS DE MÃES ESTUDANTES DA EJA DO CEEBJA PROF. PASCHOAL SALLES ROSA, EM PONTA GROSSA - PR</t>
+          <t>Uma leitura de Aya de Yopugon no ensino de literatura francófona</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5868,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5763,12 +5878,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5795,7 +5910,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5805,7 +5920,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5847,7 +5962,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5894,7 +6009,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5904,12 +6019,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellen Andrade </t>
+          <t>Ana Carolina Troyner Yamamoto</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
+          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
         </is>
       </c>
     </row>
@@ -5931,12 +6046,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5946,12 +6061,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ana Carolina Troyner Yamamoto</t>
+          <t xml:space="preserve">Ellen Andrade </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Entre o erotismo e a coerção: a legibilidade da violência sexual em O Cortiço, de Aluísio Azevedo</t>
+          <t>Do amor à agressão: uma análise da representação da violência contra a mulher na obra Medeia Morta, de Claudia Lemes</t>
         </is>
       </c>
     </row>
@@ -5978,7 +6093,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6000,7 +6115,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LINCOLN FELIPE FREITAS</t>
+          <t>Leonardo S. Carrera Guisantes</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6020,7 +6135,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6030,24 +6145,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Naiane Maria de Lima</t>
+          <t>Jackson Yuri Machado de Paula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
+          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Leonardo S. Carrera Guisantes</t>
+          <t>Ligia Paula Couto</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6057,12 +6172,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6072,19 +6187,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Jackson Yuri Machado de Paula</t>
+          <t>Leonilda de Oliveira Antunes</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>O erotismo como estrutura literária em A fúria do corpo, de João  Gilberto Noll</t>
+          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ligia Paula Couto</t>
+          <t>Lincoln Felipe Freitas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6104,7 +6219,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6114,12 +6229,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Leonilda de Oliveira Antunes</t>
+          <t>Rodrigo Vaz Alvarez Gonzales</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
+          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6246,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6141,12 +6256,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6156,12 +6271,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Estefany Ferreira Carvalho</t>
+          <t>Naiane Maria de Lima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
+          <t xml:space="preserve">OS LIMITES DA VEROSSIMILHANÇA EM TUDO É RIO, DE CARLA MADEIRA   </t>
         </is>
       </c>
     </row>
@@ -6173,7 +6288,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6183,12 +6298,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6198,12 +6313,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rodrigo Vaz Alvarez Gonzales</t>
+          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
+          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
         </is>
       </c>
     </row>
@@ -6225,12 +6340,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6240,12 +6355,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
+          <t>Estefany Ferreira Carvalho</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">A FORMAÇÃO DO HERÓI IMPROVÁVEL EM O HOBBIT: UMA ANÁLISE DA TRAJETÓRIA HEROICA DE BILBO BOLSEIRO  </t>
+          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6387,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6294,12 +6409,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
+          <t>Marcelo Oliveira Bleme</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6309,27 +6424,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>TILSP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leonilda de Oliveira Antunes</t>
+          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
+          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
         </is>
       </c>
     </row>
@@ -6351,12 +6466,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6366,12 +6481,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rafael Milek Weinert</t>
+          <t>Leonilda de Oliveira Antunes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
+          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6498,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6393,34 +6508,34 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Oziel dos Santos Martins</t>
+          <t>Rafael Milek Weinert</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
+          <t>A LETRA DE MÚSICA COMO OBJETO LITERÁRIO: UMA LEITURA INTERMIDIÁTICA ENTRE BOB DYLAN E ON THE ROAD, DE JACK KEROUAC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marcos Barbosa Carreira</t>
+          <t>Marco Aurélio de Souza</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6435,7 +6550,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6445,29 +6560,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
+          <t>Oziel dos Santos Martins</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
+          <t>O ENSINO DE LITERATURA NO 3º ANO DO ENSINO MÉDIO: UMA ANÁLISE COMPARATIVA ENTRE DOCUMENTOS CURRICULARES E AS QUESTÕES DE  LITERATURA DA PROVA PARANÁ MAIS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Maria Auxiliadora Bezerra de Araújo</t>
+          <t>Marcos Barbosa Carreira</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6482,29 +6597,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
+          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
+          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Marina Zavadzki</t>
+          <t>Maria Auxiliadora Bezerra de Araújo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6519,12 +6634,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6534,24 +6649,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ESTELA MARTINS EIDAM</t>
+          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
+          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Márcia Cristina do Carmo</t>
+          <t>Marina Zavadzki</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6561,12 +6676,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6576,19 +6691,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Juliana da Silva Carneiro</t>
+          <t>ESTELA MARTINS EIDAM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
+          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Névio de Campos</t>
+          <t>Márcia Cristina do Carmo</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6603,12 +6718,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6618,24 +6733,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lidiane Patrine Mendes Batista</t>
+          <t>Juliana da Silva Carneiro</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
+          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Paola Scheifer</t>
+          <t>Névio de Campos</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6645,12 +6760,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6660,24 +6775,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nicole Cristina Pokczyva</t>
+          <t>Lidiane Patrine Mendes Batista</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
+          <t>A Crítica Feminista de Virginia Woolf em Três Guinéus: a sociedade das Outsiders x o Patriarcado e o Militarismo</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>Paola Scheifer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6687,27 +6802,27 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Juliana da Silva Carneiro</t>
+          <t>Nicole Cristina Pokczyva</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
+          <t>A identidade em posição: espaço e desconstrução identitária em Medo e submissão, de Amélie Nothomb</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6834,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6729,7 +6844,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6744,12 +6859,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
+          <t>Juliana da Silva Carneiro</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
+          <t>O que é acolher no contexto de ensino de Língua Portuguesa para Migrantes?</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6886,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6798,12 +6913,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Patricia Barreto Mainardi Maeso</t>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6813,27 +6928,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FERNANDA DA LUZ BATISTA</t>
+          <t xml:space="preserve">João Luis Rodrigues  Machado </t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Mulheres negras, violência e resistência: corpo, voz e autonomia em dois contos de Conceição Evaristo</t>
+          <t>A EXTENSÃO UNIVERSITÁRIA E O ENSINO DE PORTUGUÊS COMO LÍNGUA DE ACOLHIMENTO E DESENVOLVIMENTO SOCIOCULTURAL PARA MIGRANTES</t>
         </is>
       </c>
     </row>
@@ -6855,39 +6970,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Giulliana Pinheiro</t>
+          <t>FERNANDA DA LUZ BATISTA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SMALL WONDERS: MATERIAL DIDÁTICO PARA O ENSINO BILÍNGUE DE CRIANÇAS DE 6 A 7 ANOS BASEADO NA ABORDAGEM COMMUNICATIVE LANGUAGE TEACHING</t>
+          <t>Mulheres negras, violência e resistência: corpo, voz e autonomia em dois contos de Conceição Evaristo</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Precisa de TILSP pois terá uma professora surda na banca</t>
+          <t>Patricia Barreto Mainardi Maeso</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6902,22 +7017,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Andréia Rosane Bueno da Silva</t>
+          <t>Giulliana Pinheiro</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>A Representação da Identidade e da Estética Surda na obra “O Despertar do Silêncio” de Shirley Vilhalva</t>
+          <t>SMALL WONDERS: MATERIAL DIDÁTICO PARA O ENSINO BILÍNGUE DE CRIANÇAS DE 6 A 7 ANOS BASEADO NA ABORDAGEM COMMUNICATIVE LANGUAGE TEACHING</t>
         </is>
       </c>
     </row>
@@ -6944,7 +7059,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6981,12 +7096,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6996,12 +7111,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Estefany Ferreira Carvalho</t>
+          <t>Rodrigo Vaz Alvarez Gonzales</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
+          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7128,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7028,7 +7143,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7038,19 +7153,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rodrigo Vaz Alvarez Gonzales</t>
+          <t>Estefany Ferreira Carvalho</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Herido e muerto, hermano. Um estudo de "Cortejo tras la toma de Bilbao"</t>
+          <t>A Lenda de Vila Velha e a cultura guarani em uma sequência didática para o Ensino de Espanhol para Crianças</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Rubia Carla da Silva</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7070,7 +7185,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7080,12 +7195,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Heridiano Pacheco dos Santos</t>
+          <t>CINTIA PIRES SZCZEREPA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
+          <t>Estudantes surdos na transição para os anos finais: análise documental do PPP de uma escola estadual em Ponta Grossa/PR</t>
         </is>
       </c>
     </row>
@@ -7107,12 +7222,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7122,12 +7237,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CINTIA PIRES SZCZEREPA</t>
+          <t>Heridiano Pacheco dos Santos</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Estudantes surdos na transição para os anos finais: análise documental do PPP de uma escola estadual em Ponta Grossa/PR</t>
+          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7254,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7149,12 +7264,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7196,34 +7311,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
+          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
+          <t xml:space="preserve">SUJEITOS NEGROS SURDOS E POLÍTICAS EDUCACIONAIS: UMA ANÁLISE DE DOCUMENTOS E MATERIAIS INSTITUCIONAIS FEDERAIS E PARANAENSES </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva e Djane Antonucci Correa</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7238,22 +7353,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
+          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUJEITOS NEGROS SURDOS E POLÍTICAS EDUCACIONAIS: UMA ANÁLISE DE DOCUMENTOS E MATERIAIS INSTITUCIONAIS FEDERAIS E PARANAENSES </t>
+          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7380,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7275,12 +7390,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7317,12 +7432,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7364,7 +7479,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7386,12 +7501,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TILSP - Valdemir</t>
+          <t>Thiago Alexandre Correa</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7401,12 +7516,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7416,24 +7531,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
+          <t>Leonilda de Oliveira Antunes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
+          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TILSP - Valdemir Pontes Vieira</t>
+          <t>Valdemir Pontes Vieira</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7443,7 +7558,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7453,7 +7568,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>TILSP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7470,7 +7585,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TILSP Marcelo Bleme</t>
+          <t>Valdemir Pontes Vieira</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7495,29 +7610,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>TILSP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
+          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Representação da menina negra surda no curta-metragem Tamara: surdidade, identidade, corpo, sonho e representatividade</t>
+          <t>Libras na sinalização escolar: elaboração e análise de um modelo bilíngue e multimodal para identificação de ambientes</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Thiago Alexandre Correa</t>
+          <t>Valeska Gracioso Carlos</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7532,22 +7647,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Leonilda de Oliveira Antunes</t>
+          <t>ESTELA MARTINS EIDAM</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>O KARAÍBA, DE DANIEL MUNDURUKU, E O CONCEITO DE ROMANCE HISTÓRICO: A LITERATURA INDÍGENA ENTRE A HISTÓRIA E A FICÇÃO</t>
+          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7674,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7569,12 +7684,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7596,12 +7711,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Valeska Gracioso Carlos</t>
+          <t>Vinícius Heitor Pereira</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7611,39 +7726,39 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ESTELA MARTINS EIDAM</t>
+          <t>NÚBIA DE BRAGA COTA MENDES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>A Permanência do Espanhol na Escola: Entre a Disputa Política e a Identidade Latino-Americana</t>
+          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Vinicius Heitor Pereira</t>
+          <t>Vinícius Heitor Pereira</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7653,27 +7768,27 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Membro</t>
+          <t>Orientador</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>NÚBIA DE BRAGA COTA MENDES</t>
+          <t>VICTOR HENRIQUE DANILENKO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tecnologias digitais e recursos de acessibilidade na trajetória acadêmica de estudantes surdos no ensino superior: revisão de escopo (2019–2026)</t>
+          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7800,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7695,12 +7810,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7722,7 +7837,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vinícius Heitor Pereira</t>
+          <t>Álvaro Kasuaki Fujihara</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7742,34 +7857,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orientador</t>
+          <t>Membro</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>VICTOR HENRIQUE DANILENKO</t>
+          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>O ensino de libras como L2 para estudantes ouvintes.</t>
+          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Álvaro Kasuaki Fujihara</t>
+          <t>Ályda Henrietta Zomer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7779,27 +7894,69 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>B212</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Membro</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Heridiano Pacheco dos Santos</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Dificuldades transformadas em potencialidades no ensino de Língua Portuguesa: concepções, metodologias e vivências com estudantes autistas e neurodivergentes na educação</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ályda Henrietta Zomer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NOTURNO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>21:05</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>B207</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>B204</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Membro</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>O OLHAR LINGUÍSTICO NA COMPUTAÇÃO: UMA ANÁLISE CRÍTICA E PRÁTICA DE PARES DE SENTENÇAS NO CORPUS SICK.</t>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guilherme Mayer Axt </t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Torcida Loca: cantos da torcida do Operário Ferroviário de Ponta Grossa</t>
         </is>
       </c>
     </row>
@@ -7872,12 +8029,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -7899,7 +8056,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7914,7 +8071,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7946,12 +8103,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7973,7 +8130,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7988,7 +8145,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8025,7 +8182,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8047,7 +8204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8057,12 +8214,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8084,7 +8241,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8099,7 +8256,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B207</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8168,7 +8325,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8195,7 +8352,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8205,12 +8362,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B203</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8247,7 +8404,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8279,12 +8436,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B204</t>
+          <t>B210</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8306,7 +8463,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8316,12 +8473,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8390,7 +8547,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8417,7 +8574,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8427,12 +8584,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8464,12 +8621,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8501,12 +8658,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8575,12 +8732,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8612,12 +8769,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8639,7 +8796,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8649,12 +8806,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8686,12 +8843,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8723,12 +8880,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B214</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8802,7 +8959,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8834,7 +8991,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8871,12 +9028,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8908,12 +9065,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8945,12 +9102,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8972,7 +9129,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8982,12 +9139,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B203</t>
+          <t>B208</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9024,7 +9181,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B207</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9056,7 +9213,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9098,7 +9255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B210</t>
+          <t>B204</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9135,7 +9292,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9167,12 +9324,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9194,7 +9351,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9204,7 +9361,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -9214,7 +9371,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva e Djane Antonucci Correa</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9314,7 +9471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9324,17 +9481,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Giulliana Pinheiro</t>
+          <t>Naiane Maria de Lima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Patricia Barreto Mainardi Maeso</t>
+          <t>Silvana Oliveira</t>
         </is>
       </c>
     </row>
@@ -9356,17 +9513,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andrey Eduardo Malinoscky</t>
+          <t>Nicole Cristina Pokczyva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Evanir Pavloski</t>
+          <t>Andréa Correa Paraiso Müller</t>
         </is>
       </c>
     </row>
@@ -9388,29 +9545,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ana Julia Ruths de Castro</t>
+          <t>Estefany Ferreira Carvalho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Evanir Pavloski</t>
+          <t>Rosangela Schardong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9420,17 +9577,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jackson Yuri Machado de Paula</t>
+          <t>Leonilda de Oliveira Antunes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eunice de Morais</t>
+          <t>Marco Aurélio de Souza</t>
         </is>
       </c>
     </row>
@@ -9452,17 +9609,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Joseanne Kanufre Pires Ferreira</t>
+          <t>Ana Julia Ruths de Castro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
+          <t>Evanir Pavloski</t>
         </is>
       </c>
     </row>
@@ -9484,17 +9641,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Estefany Ferreira Carvalho</t>
+          <t>Rafael Milek Weinert</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosangela Schardong</t>
+          <t>Marco Aurélio de Souza</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9516,17 +9673,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodrigo Vaz Alvarez Gonzales</t>
+          <t>ESTELA MARTINS EIDAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosangela Schardong</t>
+          <t>Valeska Gracioso Carlos</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9710,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lohan Vinícius de Oliveira</t>
+          <t>Giulliana Pinheiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daniel van der Broocke de Oliveira Gomes</t>
+          <t>Patricia Barreto Mainardi Maeso</t>
         </is>
       </c>
     </row>
@@ -9585,12 +9742,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NÚBIA DE BRAGA COTA MENDES</t>
+          <t>EMANUELLY MAUDA SCOS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andressa França</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9774,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
+          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9649,7 +9806,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PALOMA TEIXEIRA DE OLIVEIRA</t>
+          <t>GISELE CRISTINA DE SOUZA LOPES CAMARGO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9681,12 +9838,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ellen Andrade</t>
+          <t>Lidiane Patrine Mendes Batista</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Keli Cristina Pacheco</t>
+          <t>Joana dArc Martins Pupo</t>
         </is>
       </c>
     </row>
@@ -9713,12 +9870,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lidiane Patrine Mendes Batista</t>
+          <t>Pamela Cristina Rodrigues</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Joana dArc Martins Pupo</t>
+          <t>Charlott Eloize Leviski</t>
         </is>
       </c>
     </row>
@@ -9745,12 +9902,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ana Carolina Troyner Yamamoto</t>
+          <t>Guilherme Mayer Axt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Keli Cristina Pacheco</t>
+          <t>Cloris Porto Torquato</t>
         </is>
       </c>
     </row>
@@ -9777,12 +9934,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanis Cristine Barros</t>
+          <t>Andrey Eduardo Malinoscky</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bhianca Moro Portella</t>
+          <t>Evanir Pavloski</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9966,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
+          <t>Oziel dos Santos Martins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
+          <t>Rosana Apolonia Harmuch</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9998,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
+          <t>Isabela Fernandes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marcos Barbosa Carreira</t>
+          <t>Daiane Cristina Pereira</t>
         </is>
       </c>
     </row>
@@ -9905,12 +10062,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EMANUELLY MAUDA SCOS</t>
+          <t>NÚBIA DE BRAGA COTA MENDES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva</t>
+          <t>Andressa França</t>
         </is>
       </c>
     </row>
@@ -9922,7 +10079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9932,17 +10089,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
+          <t>Julia  Soares Nadal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rúbia Carla da Silva e Djane Antonucci Correa</t>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
         </is>
       </c>
     </row>
@@ -9964,17 +10121,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Isabela Fernandes</t>
+          <t>SERGIO DE SOUZA CAMPISTA JUNIOR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daiane Cristina Pereira</t>
+          <t>Rúbia Carla da Silva</t>
         </is>
       </c>
     </row>
@@ -9996,24 +10153,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Naiane Maria de Lima</t>
+          <t>João Luis Rodrigues  Machado</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silvana Oliveira</t>
+          <t>Pascoalina Bailon de Oliveira Saleh</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B208</t>
+          <t>B209</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10028,17 +10185,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nicole Cristina Pokczyva</t>
+          <t>Andréia Rosane Bueno da Silva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Andréa Correa Paraiso Müller</t>
+          <t>Vinícius Heitor Pereira</t>
         </is>
       </c>
     </row>
@@ -10065,12 +10222,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guilherme Mayer Axt</t>
+          <t>Ana Carolina Troyner Yamamoto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cloris Porto Torquato</t>
+          <t>Keli Cristina Pacheco</t>
         </is>
       </c>
     </row>
@@ -10097,12 +10254,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pamela Cristina Rodrigues</t>
+          <t>Ellen Andrade</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlott Eloize Leviski</t>
+          <t>Keli Cristina Pacheco</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10318,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
+          <t>ALÍA REBECA MOREIRA E SUBTIL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Carlos André Ferreira</t>
+          <t>Charlott Eloize Leviski</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10350,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oziel dos Santos Martins</t>
+          <t>ELOINA APARECIDA MONTEIRO DOS SANTOS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosana Apolonia Harmuch</t>
+          <t>Carlos André Ferreira</t>
         </is>
       </c>
     </row>
@@ -10257,12 +10414,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leonilda de Oliveira Antunes</t>
+          <t>Alanis Cristine Barros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
+          <t>Bhianca Moro Portella</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10446,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Andréia Rosane Bueno da Silva</t>
+          <t>Heridiano Pacheco dos Santos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vinícius Heitor Pereira</t>
+          <t>Fabiana Simeoni Avais</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10478,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rafael Milek Weinert</t>
+          <t>CARLA ANDRESSA RODRIGUES DE ASSUNÇÃO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marco Aurélio de Souza</t>
+          <t>Marcos Barbosa Carreira</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10510,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heridiano Pacheco dos Santos</t>
+          <t>Rodrigo Vaz Alvarez Gonzales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fabiana Simeoni Avais</t>
+          <t>Rosangela Schardong</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10606,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ESTELA MARTINS EIDAM</t>
+          <t>Lohan Vinícius de Oliveira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valeska Gracioso Carlos</t>
+          <t>Daniel van der Broocke de Oliveira Gomes</t>
         </is>
       </c>
     </row>
@@ -10481,12 +10638,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>João Luis Rodrigues  Machado</t>
+          <t>Jackson Yuri Machado de Paula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>Eunice de Morais</t>
         </is>
       </c>
     </row>
@@ -10513,12 +10670,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Julia  Soares Nadal</t>
+          <t>Joseanne Kanufre Pires Ferreira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pascoalina Bailon de Oliveira Saleh</t>
+          <t>Andréa Correa Paraiso Müller</t>
         </is>
       </c>
     </row>
